--- a/메모.xlsx
+++ b/메모.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\f2_telecom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E20917E-F5ED-43AE-8AE9-98F8A8306AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D16BA49B-58A8-46C2-B9A6-4E4CE38AE693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21810" windowHeight="15345" activeTab="3" xr2:uid="{F4C60120-7625-4569-B73A-038EDEEC919B}"/>
+    <workbookView xWindow="2805" yWindow="645" windowWidth="28800" windowHeight="15345" activeTab="4" xr2:uid="{F4C60120-7625-4569-B73A-038EDEEC919B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="주소개별업데이트" sheetId="2" r:id="rId2"/>
     <sheet name="레벨" sheetId="3" r:id="rId3"/>
     <sheet name="사용자" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="95">
   <si>
     <t>파이어베이스 스토리지(Storage)에 파일 올리기</t>
   </si>
@@ -924,13 +925,328 @@
   <si>
     <t>문서삭제</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>config</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 문서의 각 필드가 앱에서 하는 일이에요. 앱 코드를 기준으로 정리했어요.</t>
+    </r>
+  </si>
+  <si>
+    <t>앱 업데이트</t>
+  </si>
+  <si>
+    <t>필드</t>
+  </si>
+  <si>
+    <t>지금 값</t>
+  </si>
+  <si>
+    <t>기능</t>
+  </si>
+  <si>
+    <t>android_ver</t>
+  </si>
+  <si>
+    <t>“1.1.5”</t>
+  </si>
+  <si>
+    <r>
+      <t>서버 앱 버전.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 직원 앱 버전보다 높으면 앱을 켤 때와 홈 화면에서 "업데이트 알림" 창을 띄워요. (1.1.4 이하 앱은 버전이 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>다르기만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 해도 창을 띄워요)</t>
+    </r>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>드라이브 링크</t>
+  </si>
+  <si>
+    <t>업데이트 창에서 **[업데이트 하기]**를 누르면 열리는 APK 다운로드 주소예요.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">⚠️ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>url</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>을 바꿔 주세요.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 지금은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>.../file/d/…/view?usp=sharing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 형태라서 누르면 다운로드가 아니라 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>드라이브 미리보기 화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>이 열려요. 아래로 바꾸면 바로 다운로드돼요.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://drive.google.com/uc?export=download&amp;id=1D8TIt9HcSA4KU3XBut2wLA69o4qMWTS0</t>
+  </si>
+  <si>
+    <t>그리고 이 파일도 공유 설정이 **”링크가 있는 모든 사용자"**로 돼 있어야 해요.</t>
+  </si>
+  <si>
+    <r>
+      <t>공지사항</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (관리자 메뉴 › 데이터 갱신 화면에서 바꿀 수 있음)</t>
+    </r>
+  </si>
+  <si>
+    <t>showNotice</t>
+  </si>
+  <si>
+    <r>
+      <t>true면 모든 직원이 앱을 켤 때 공지 창이 떠요.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> false면 안 떠요.</t>
+    </r>
+  </si>
+  <si>
+    <t>noticeTitle</t>
+  </si>
+  <si>
+    <t>"테스트중입니다"</t>
+  </si>
+  <si>
+    <t>공지 창 제목</t>
+  </si>
+  <si>
+    <t>noticeContent</t>
+  </si>
+  <si>
+    <t>"추가기능요청 건의해주세요…"</t>
+  </si>
+  <si>
+    <t>공지 창 내용</t>
+  </si>
+  <si>
+    <r>
+      <t>주소록 데이터(국소 CSV) 업데이트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (관리자 메뉴 › 데이터 갱신 화면에서 바꿀 수 있음)</t>
+    </r>
+  </si>
+  <si>
+    <t>csvUrl</t>
+  </si>
+  <si>
+    <t>“” (비어 있음)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">새 주소록 CSV 파일의 다운로드 주소. 비어 있으면 주소록 업데이트 기능이 동작하지 않고, 사용자 관리의 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"최신 데이터 개별 전송"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 버튼도 오류가 나요.</t>
+    </r>
+  </si>
+  <si>
+    <t>dataVersion</t>
+  </si>
+  <si>
+    <t>“1.0”</t>
+  </si>
+  <si>
+    <t>주소록 데이터 버전. 직원 폰에 저장된 버전과 다르면 다운로드 창을 띄워요.</t>
+  </si>
+  <si>
+    <t>forceUpdate</t>
+  </si>
+  <si>
+    <r>
+      <t>true면 모든 직원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>에게 "새 주소록 데이터 다운로드" 창이 떠요. false면 개별 전송만 돼요.</t>
+    </r>
+  </si>
+  <si>
+    <t>lastUpdated</t>
+  </si>
+  <si>
+    <t>데이터 갱신 화면에서 마지막으로 저장한 시각이에요. 기록용이라 앱 동작에는 영향이 없어요.</t>
+  </si>
+  <si>
+    <t>쓰지 않는 필드</t>
+  </si>
+  <si>
+    <t>globalUpdateUrl</t>
+  </si>
+  <si>
+    <t>현재 앱 코드 어디에서도 읽지 않아요. 예전에 쓰던 값으로 보여요. 둬도 문제없어요.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1003,6 +1319,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF14181F"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1029,7 +1353,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1060,6 +1384,30 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1076,6 +1424,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>2915602</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>201691</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45C51ABA-C9D9-2DA6-49D1-8404ABD13A58}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7905750"/>
+          <a:ext cx="6820852" cy="11936491"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1848,4 +2245,219 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7585DB60-4B74-48C0-A99F-1DCE91FF853B}">
+  <dimension ref="A2:C61"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="51.25" customWidth="1"/>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="3" max="3" width="128.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:3">
+      <c r="A2" s="10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="15" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="12" t="b">
+        <v>1</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="25.5">
+      <c r="A21" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="25.5">
+      <c r="A27" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="25.5">
+      <c r="A28" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B28" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="25.5">
+      <c r="A29" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" s="16">
+        <v>46006</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="25.5">
+      <c r="A34" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="60" spans="3:3">
+      <c r="C60" s="17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="3:3">
+      <c r="C61" s="17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>